--- a/vocabulary/词汇录入表.xlsx
+++ b/vocabulary/词汇录入表.xlsx
@@ -2,49 +2,402 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="22980" windowHeight="11480" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词汇录入表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'词汇录入表'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'词汇录入表'!$A$1:$F$8</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="26">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Mongolian Baiti"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="Microsoft YaHei"/>
-      <sz val="11"/>
+      <charset val="134"/>
+      <sz val="20"/>
     </font>
     <font>
       <name val="Mongolian Baiti"/>
-      <sz val="16"/>
+      <charset val="134"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -52,21 +405,326 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -419,7 +1077,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -429,141 +1086,428 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="26"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="5.54545454545455" customWidth="1" style="9" min="1" max="1"/>
+    <col width="16" customWidth="1" style="9" min="2" max="2"/>
+    <col width="18" customWidth="1" style="2" min="3" max="3"/>
+    <col width="18" customWidth="1" style="8" min="4" max="4"/>
+    <col width="40" customWidth="1" style="8" min="5" max="5"/>
+    <col width="10" customWidth="1" style="8" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>联合转写</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>蒙文词形</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>释义</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>书目或作者+页码</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>monggol</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>ᠮᠣᠩᠭᠣᠯ</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>蒙古</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>《蒙古语基础》p.12</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>最好写上</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="n"/>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>tabu</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>ᠲᠠᠪᠤ</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>五</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>不知道就写“未知”</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n"/>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>xurud</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>ᠬᠤᠷᠤᠳ</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>奶豆腐</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>懒得写可以不写</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>完成</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>tabu</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>ᠲᠠᠪᠤ</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>五</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>《蒙古语基础》p.30</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>完成</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>xurud</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>ᠬᠤᠷᠤᠳ</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>奶豆腐</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>高莲花《蒙古语短语结构》p.45</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>待定</t>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>xöxexota</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>ᠬᠥᠬᠡᠬᠣᠲᠠ</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>不确定</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>bošog-a</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>ᠪᠣᠱᠣᠭ ᠠ</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>门槛</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>有后缀？</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>šölö</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>ᠱᠥᠯᠥ</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>肉汤</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>ǰun</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>ᠵᠤᠨ</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>夏天</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>lhasa</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>ᡀᠠᠰᠠ</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>拉萨</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>taulai</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>ᠲᠠᠤᠯᠠᠢ</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>兔子</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>agula</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>ᠠᠭᠤᠯᠠ</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>山</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>üǰüg</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>ᠦᠵᠦᠭ</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>钢笔</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>bey-e</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>ᠪᠡᠶ ᠡ</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>身体</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>有后缀？</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>abu</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>ᠠᠪᠤ</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>父亲</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>banana</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>ᠪᠠᠨᠠᠨᠠ</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>香蕉</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>xadag</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>ᠬᠠᠳᠠᠭ</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>哈达</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>gurba</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>ᠭᠤᠷᠪᠠ</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>三</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>nugusu</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>ᠨᠤᠭᠤᠰᠤ</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>鸭子</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:F8"/>
   <dataValidations count="1">
     <dataValidation sqref="F2:F2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完成,待定"</formula1>
